--- a/data/baidu/china_sports.xlsx
+++ b/data/baidu/china_sports.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2008年第29届北京奥运会开幕式</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2008年第29届北京奥运会开幕式</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -660,16 +668,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>少林足球</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>少林足球</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -734,24 +750,30 @@
           <t>https://movie.douban.com/subject/20388223/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>18673.57142857143</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>激战</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>激战</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -814,16 +836,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>大李小李和老李</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>大李小李和老李</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -888,24 +918,30 @@
           <t>https://movie.douban.com/subject/36369452/</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>11272.85714285714</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>飞驰人生2</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>飞驰人生2</t>
+        </is>
+      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -965,24 +1001,30 @@
           <t>https://movie.douban.com/subject/36081094/</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>9615.714285714286</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>热辣滚烫</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>热辣滚烫</t>
+        </is>
+      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1042,24 +1084,30 @@
           <t>https://movie.douban.com/subject/5446197/</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>3457.571428571428</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>铁拳</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>铁拳</t>
+        </is>
+      </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1122,16 +1170,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3658518676, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>翻滚吧！阿信</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>翻滚吧！阿信</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1196,24 +1252,30 @@
           <t>https://movie.douban.com/subject/37311135/</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>10722.28571428571</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>飞驰人生3</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>飞驰人生3</t>
+        </is>
+      </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1273,24 +1335,30 @@
           <t>https://movie.douban.com/subject/25853727/</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>55289.85714285714</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>破风</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>破风</t>
+        </is>
+      </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1350,24 +1418,30 @@
           <t>https://movie.douban.com/subject/35030151/</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>4781.142857142857</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>五个扑水的少年</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>五个扑水的少年</t>
+        </is>
+      </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1427,24 +1501,30 @@
           <t>https://movie.douban.com/subject/25809384/</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>7286.428571428572</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>极盗者</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>极盗者</t>
+        </is>
+      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -1504,24 +1584,30 @@
           <t>https://movie.douban.com/subject/30128916/</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>6439.285714285715</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>夺冠</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>夺冠</t>
+        </is>
+      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1581,24 +1667,30 @@
           <t>https://movie.douban.com/subject/30163509/</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>15574.57142857143</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>飞驰人生</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>飞驰人生</t>
+        </is>
+      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -1661,16 +1753,24 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>龙少爷</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>龙少爷</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -1735,21 +1835,27 @@
           <t>https://movie.douban.com/subject/30323380/</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>中国乒乓之绝地反击</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>中国乒乓之绝地反击</t>
+        </is>
+      </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1812,24 +1918,30 @@
           <t>https://movie.douban.com/subject/35882742/</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>1342.142857142857</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>好像也没那么热血沸腾</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>好像也没那么热血沸腾</t>
+        </is>
+      </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1889,24 +2001,30 @@
           <t>https://movie.douban.com/subject/32568661/</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>3787.142857142857</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>妈妈的神奇小子</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>妈妈的神奇小子</t>
+        </is>
+      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1966,24 +2084,30 @@
           <t>https://movie.douban.com/subject/35608160/</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>10619.42857142857</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之筐出未来</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>喜羊羊与灰太狼之筐出未来</t>
+        </is>
+      </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -2046,16 +2170,24 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>波牛</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>波牛</t>
+        </is>
+      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
@@ -2123,16 +2255,24 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>京都球侠</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>京都球侠</t>
+        </is>
+      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -2200,16 +2340,24 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>黑眼睛</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>黑眼睛</t>
+        </is>
+      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -2277,16 +2425,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>女篮5号</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>女篮5号</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2351,24 +2507,30 @@
           <t>https://movie.douban.com/subject/30391228/</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="n">
+        <v>416.5714285714286</v>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>了不起的老爸</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>了不起的老爸</t>
+        </is>
+      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2428,24 +2590,30 @@
           <t>https://movie.douban.com/subject/11599168/</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>328.2857142857143</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>志气</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>志气</t>
+        </is>
+      </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -2508,16 +2676,24 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>功夫梦</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>功夫梦</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -2585,16 +2761,24 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>沙鸥</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>沙鸥</t>
+        </is>
+      </c>
       <c r="T28" t="n">
         <v>0</v>
       </c>
@@ -2662,16 +2846,24 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>一个人的奥林匹克</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>一个人的奥林匹克</t>
+        </is>
+      </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
@@ -2739,16 +2931,24 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>近在咫尺的爱恋</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>近在咫尺的爱恋</t>
+        </is>
+      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -2813,24 +3013,30 @@
           <t>https://movie.douban.com/subject/25903033/</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>11097</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>我是马布里</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>我是马布里</t>
+        </is>
+      </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -2890,24 +3096,30 @@
           <t>https://movie.douban.com/subject/26704592/</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>878.8571428571429</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>点五步</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>点五步</t>
+        </is>
+      </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -2970,16 +3182,24 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>买买提的2008</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>买买提的2008</t>
+        </is>
+      </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
@@ -3044,24 +3264,30 @@
           <t>https://movie.douban.com/subject/30328825/</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>152</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>下半场</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>下半场</t>
+        </is>
+      </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -3124,16 +3350,24 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>单车上路</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>单车上路</t>
+        </is>
+      </c>
       <c r="T35" t="n">
         <v>0</v>
       </c>
@@ -3198,24 +3432,30 @@
           <t>https://movie.douban.com/subject/35207868/</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>6265.428571428572</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>陈翔六点半之民间高手</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>陈翔六点半之民间高手</t>
+        </is>
+      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -3278,16 +3518,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>扣篮对决</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>扣篮对决</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3355,16 +3603,24 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>玩酷青春</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>玩酷青春</t>
+        </is>
+      </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
@@ -3429,21 +3685,27 @@
           <t>https://movie.douban.com/subject/34834554/</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>点点星光</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>点点星光</t>
+        </is>
+      </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3509,16 +3771,24 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>无野之城</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>无野之城</t>
+        </is>
+      </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
@@ -3583,24 +3853,30 @@
           <t>https://movie.douban.com/subject/27006898/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>1115.714285714286</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>空手道</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>空手道</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3663,16 +3939,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>大灌篮</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>大灌篮</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3740,16 +4024,24 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>奇怪的球赛</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>奇怪的球赛</t>
+        </is>
+      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
@@ -3814,21 +4106,27 @@
           <t>https://movie.douban.com/subject/36088962/</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>黑鹰少年</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>黑鹰少年</t>
+        </is>
+      </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -3891,24 +4189,30 @@
           <t>https://movie.douban.com/subject/5919333/</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>11169.71428571429</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>大明猩</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>大明猩</t>
+        </is>
+      </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -3968,24 +4272,30 @@
           <t>https://movie.douban.com/subject/6946777/</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>4692.714285714285</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>跑出一片天</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>跑出一片天</t>
+        </is>
+      </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4045,24 +4355,30 @@
           <t>https://movie.douban.com/subject/26765405/</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>2816.714285714286</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>一路向南</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>一路向南</t>
+        </is>
+      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -4125,16 +4441,24 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3665598003, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -4202,16 +4526,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>破冰</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>破冰</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4279,16 +4611,24 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>高中锋，矮教练</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>高中锋，矮教练</t>
+        </is>
+      </c>
       <c r="T50" t="n">
         <v>0</v>
       </c>
@@ -4356,16 +4696,24 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>流浪汉世界杯</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>流浪汉世界杯</t>
+        </is>
+      </c>
       <c r="T51" t="n">
         <v>0</v>
       </c>
@@ -4430,24 +4778,30 @@
           <t>https://movie.douban.com/subject/27119392/</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>2035.142857142857</v>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>狼图腾：一人一生一座城</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>狼图腾</t>
+        </is>
+      </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -4510,16 +4864,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3666143002, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>屋顶足球</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>屋顶足球</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4587,16 +4949,24 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>女跳水队员</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>女跳水队员</t>
+        </is>
+      </c>
       <c r="T54" t="n">
         <v>0</v>
       </c>
@@ -4664,16 +5034,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>出水芙蓉</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>出水芙蓉</t>
+        </is>
+      </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -4741,16 +5119,24 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>超级无敌追女仔</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>超级无敌追女仔</t>
+        </is>
+      </c>
       <c r="T56" t="n">
         <v>0</v>
       </c>
@@ -4818,16 +5204,24 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>冰与火</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>冰与火</t>
+        </is>
+      </c>
       <c r="T57" t="n">
         <v>0</v>
       </c>
@@ -4892,24 +5286,30 @@
           <t>https://movie.douban.com/subject/34917447/</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>7650.428571428572</v>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>超越</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>超越</t>
+        </is>
+      </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -4972,16 +5372,24 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3666567952, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>激情跳水梦</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>激情跳水梦</t>
+        </is>
+      </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -5049,16 +5457,24 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>巧克力重击</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>巧克力重击</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
@@ -5126,16 +5542,24 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>哈罗！比基尼</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>哈罗！比基尼</t>
+        </is>
+      </c>
       <c r="T61" t="n">
         <v>0</v>
       </c>
@@ -5203,16 +5627,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3666774191, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>父子拳王</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>父子拳王</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5280,16 +5712,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>冰上姐妹</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>冰上姐妹</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5357,16 +5797,24 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3666976482, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>别叫我“赌神”</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>别叫我“赌神”</t>
+        </is>
+      </c>
       <c r="T64" t="n">
         <v>0</v>
       </c>
@@ -5431,24 +5879,30 @@
           <t>https://movie.douban.com/subject/19977901/</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>209.4285714285714</v>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>许海峰的枪</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>许海峰的枪</t>
+        </is>
+      </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -5508,21 +5962,27 @@
           <t>https://movie.douban.com/subject/35017520/</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>疯狂老爹</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>疯狂老爹</t>
+        </is>
+      </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -5585,21 +6045,27 @@
           <t>https://movie.douban.com/subject/27069788/</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>旋风女队</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>旋风女队</t>
+        </is>
+      </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5665,16 +6131,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3668074355, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>深宵闪避球</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>深宵闪避球</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5742,16 +6216,24 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3668284320, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>出拳吧，妈妈</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>出拳吧，妈妈</t>
+        </is>
+      </c>
       <c r="T69" t="n">
         <v>0</v>
       </c>
@@ -5816,24 +6298,30 @@
           <t>https://movie.douban.com/subject/27132180/</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>2117.285714285714</v>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>我的拳王男友</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>我的拳王男友</t>
+        </is>
+      </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -5893,24 +6381,30 @@
           <t>https://movie.douban.com/subject/10799138/</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>132</v>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>球来就打</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>球来就打</t>
+        </is>
+      </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
@@ -5973,16 +6467,24 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3669038089, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>踢球吧少年</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>踢球吧少年</t>
+        </is>
+      </c>
       <c r="T72" t="n">
         <v>0</v>
       </c>
@@ -6050,16 +6552,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>篮球公园</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>篮球公园</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6124,24 +6634,30 @@
           <t>https://movie.douban.com/subject/34926591/</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>10212.85714285714</v>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>快进者</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>快进者</t>
+        </is>
+      </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -6201,24 +6717,30 @@
           <t>https://movie.douban.com/subject/20381251/</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>682.8571428571429</v>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>金牌流浪狗</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>金牌流浪狗</t>
+        </is>
+      </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -6278,24 +6800,30 @@
           <t>https://movie.douban.com/subject/5319803/</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>2701.428571428572</v>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>热浪球爱战</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>热浪球爱战</t>
+        </is>
+      </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -6358,16 +6886,24 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3670109494, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>刺心切骨</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>刺心切骨</t>
+        </is>
+      </c>
       <c r="T77" t="n">
         <v>0</v>
       </c>
@@ -6432,24 +6968,30 @@
           <t>https://movie.douban.com/subject/30279972/</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>6318.285714285715</v>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>叱咤风云</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>叱咤风云</t>
+        </is>
+      </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -6512,16 +7054,24 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3670663834, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>冠军的心</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>冠军的心</t>
+        </is>
+      </c>
       <c r="T79" t="n">
         <v>0</v>
       </c>
@@ -6586,24 +7136,30 @@
           <t>https://movie.douban.com/subject/30242130/</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>2703.285714285714</v>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>杀手世界杯</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>杀手世界杯</t>
+        </is>
+      </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -6666,16 +7222,24 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3671281474, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>野夏天</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>野夏天</t>
+        </is>
+      </c>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -6740,24 +7304,30 @@
           <t>https://movie.douban.com/subject/26844130/</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>963.2857142857143</v>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>击战</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>击战</t>
+        </is>
+      </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -6820,16 +7390,24 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>missing_release_date</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
+          <t>上映日期缺失或无法解析</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>电竞高校</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>电竞高校</t>
+        </is>
+      </c>
       <c r="T83" t="n">
         <v>0</v>
       </c>
@@ -6897,16 +7475,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>少林少女</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>少林少女</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -6971,24 +7557,30 @@
           <t>https://movie.douban.com/subject/27098659/</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>4984.142857142857</v>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>甩尾王</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>甩尾王</t>
+        </is>
+      </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -7051,16 +7643,24 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 3698389640, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>舍身技</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>舍身技</t>
+        </is>
+      </c>
       <c r="T86" t="n">
         <v>0</v>
       </c>
@@ -7125,24 +7725,30 @@
           <t>https://movie.douban.com/subject/26413404/</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>726.8571428571429</v>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>蹴鞠</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>蹴鞠</t>
+        </is>
+      </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
@@ -7202,24 +7808,30 @@
           <t>https://movie.douban.com/subject/26547005/</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>1418.571428571429</v>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>笑林足球</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>笑林足球</t>
+        </is>
+      </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
@@ -7279,24 +7891,30 @@
           <t>https://movie.douban.com/subject/5044748/</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
+      <c r="O89" t="n">
+        <v>21195.14285714286</v>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>神奇</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>神奇</t>
+        </is>
+      </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
